--- a/AAII_Financials/Quarterly/VIAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VIAO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -749,25 +749,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>59600</v>
+        <v>59700</v>
       </c>
       <c r="E8" s="3">
-        <v>68200</v>
+        <v>68400</v>
       </c>
       <c r="F8" s="3">
-        <v>52200</v>
+        <v>52300</v>
       </c>
       <c r="G8" s="3">
-        <v>57200</v>
+        <v>57300</v>
       </c>
       <c r="H8" s="3">
-        <v>50200</v>
+        <v>50400</v>
       </c>
       <c r="I8" s="3">
-        <v>53600</v>
+        <v>53800</v>
       </c>
       <c r="J8" s="3">
-        <v>47400</v>
+        <v>47500</v>
       </c>
       <c r="K8" s="3">
         <v>43700</v>
@@ -805,25 +805,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>49700</v>
+        <v>49800</v>
       </c>
       <c r="E9" s="3">
-        <v>62400</v>
+        <v>62600</v>
       </c>
       <c r="F9" s="3">
-        <v>47700</v>
+        <v>47900</v>
       </c>
       <c r="G9" s="3">
-        <v>52900</v>
+        <v>53100</v>
       </c>
       <c r="H9" s="3">
-        <v>47200</v>
+        <v>47300</v>
       </c>
       <c r="I9" s="3">
-        <v>46200</v>
+        <v>46400</v>
       </c>
       <c r="J9" s="3">
-        <v>40800</v>
+        <v>40900</v>
       </c>
       <c r="K9" s="3">
         <v>38700</v>
@@ -867,7 +867,7 @@
         <v>5900</v>
       </c>
       <c r="F10" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="G10" s="3">
         <v>4200</v>
@@ -1182,25 +1182,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>64300</v>
+        <v>64500</v>
       </c>
       <c r="E17" s="3">
-        <v>66000</v>
+        <v>66200</v>
       </c>
       <c r="F17" s="3">
-        <v>53500</v>
+        <v>53600</v>
       </c>
       <c r="G17" s="3">
-        <v>60500</v>
+        <v>60700</v>
       </c>
       <c r="H17" s="3">
-        <v>56300</v>
+        <v>56500</v>
       </c>
       <c r="I17" s="3">
-        <v>52800</v>
+        <v>53000</v>
       </c>
       <c r="J17" s="3">
-        <v>50800</v>
+        <v>50900</v>
       </c>
       <c r="K17" s="3">
         <v>43000</v>
@@ -1652,7 +1652,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6800</v>
+        <v>-6900</v>
       </c>
       <c r="E26" s="3">
         <v>1300</v>
@@ -1670,7 +1670,7 @@
         <v>200</v>
       </c>
       <c r="J26" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="K26" s="3">
         <v>200</v>
@@ -1708,7 +1708,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6800</v>
+        <v>-6900</v>
       </c>
       <c r="E27" s="3">
         <v>1300</v>
@@ -1726,7 +1726,7 @@
         <v>100</v>
       </c>
       <c r="J27" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="K27" s="3">
         <v>200</v>
@@ -2044,7 +2044,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6800</v>
+        <v>-6900</v>
       </c>
       <c r="E33" s="3">
         <v>1300</v>
@@ -2062,7 +2062,7 @@
         <v>100</v>
       </c>
       <c r="J33" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="K33" s="3">
         <v>200</v>
@@ -2156,7 +2156,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6800</v>
+        <v>-6900</v>
       </c>
       <c r="E35" s="3">
         <v>1300</v>
@@ -2174,7 +2174,7 @@
         <v>100</v>
       </c>
       <c r="J35" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="K35" s="3">
         <v>200</v>
@@ -2317,25 +2317,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>48200</v>
+        <v>48300</v>
       </c>
       <c r="E41" s="3">
-        <v>58900</v>
+        <v>59100</v>
       </c>
       <c r="F41" s="3">
-        <v>57800</v>
+        <v>58000</v>
       </c>
       <c r="G41" s="3">
-        <v>51100</v>
+        <v>51200</v>
       </c>
       <c r="H41" s="3">
-        <v>62900</v>
+        <v>63100</v>
       </c>
       <c r="I41" s="3">
-        <v>59500</v>
+        <v>59600</v>
       </c>
       <c r="J41" s="3">
-        <v>64400</v>
+        <v>64600</v>
       </c>
       <c r="K41" s="3">
         <v>78700</v>
@@ -2429,25 +2429,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>25600</v>
+        <v>25700</v>
       </c>
       <c r="E43" s="3">
-        <v>36800</v>
+        <v>36900</v>
       </c>
       <c r="F43" s="3">
-        <v>34400</v>
+        <v>34500</v>
       </c>
       <c r="G43" s="3">
-        <v>38400</v>
+        <v>38500</v>
       </c>
       <c r="H43" s="3">
-        <v>34400</v>
+        <v>34500</v>
       </c>
       <c r="I43" s="3">
-        <v>40300</v>
+        <v>40400</v>
       </c>
       <c r="J43" s="3">
-        <v>33600</v>
+        <v>33700</v>
       </c>
       <c r="K43" s="3">
         <v>33000</v>
@@ -2488,22 +2488,22 @@
         <v>24000</v>
       </c>
       <c r="E44" s="3">
-        <v>34700</v>
+        <v>34800</v>
       </c>
       <c r="F44" s="3">
-        <v>43700</v>
+        <v>43900</v>
       </c>
       <c r="G44" s="3">
-        <v>41200</v>
+        <v>41300</v>
       </c>
       <c r="H44" s="3">
-        <v>38900</v>
+        <v>39000</v>
       </c>
       <c r="I44" s="3">
-        <v>35400</v>
+        <v>35500</v>
       </c>
       <c r="J44" s="3">
-        <v>30900</v>
+        <v>31000</v>
       </c>
       <c r="K44" s="3">
         <v>25700</v>
@@ -2541,10 +2541,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13300</v>
+        <v>13400</v>
       </c>
       <c r="E45" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F45" s="3">
         <v>7900</v>
@@ -2597,25 +2597,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>119800</v>
+        <v>120100</v>
       </c>
       <c r="E46" s="3">
-        <v>139700</v>
+        <v>140100</v>
       </c>
       <c r="F46" s="3">
-        <v>143900</v>
+        <v>144300</v>
       </c>
       <c r="G46" s="3">
-        <v>139100</v>
+        <v>139500</v>
       </c>
       <c r="H46" s="3">
-        <v>145200</v>
+        <v>145600</v>
       </c>
       <c r="I46" s="3">
-        <v>139700</v>
+        <v>140100</v>
       </c>
       <c r="J46" s="3">
-        <v>135400</v>
+        <v>135800</v>
       </c>
       <c r="K46" s="3">
         <v>141000</v>
@@ -2712,13 +2712,13 @@
         <v>22700</v>
       </c>
       <c r="E48" s="3">
-        <v>23000</v>
+        <v>23100</v>
       </c>
       <c r="F48" s="3">
-        <v>23200</v>
+        <v>23300</v>
       </c>
       <c r="G48" s="3">
-        <v>23500</v>
+        <v>23600</v>
       </c>
       <c r="H48" s="3">
         <v>23400</v>
@@ -3045,25 +3045,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>147900</v>
+        <v>148300</v>
       </c>
       <c r="E54" s="3">
-        <v>168800</v>
+        <v>169300</v>
       </c>
       <c r="F54" s="3">
-        <v>173700</v>
+        <v>174200</v>
       </c>
       <c r="G54" s="3">
-        <v>169200</v>
+        <v>169600</v>
       </c>
       <c r="H54" s="3">
-        <v>175400</v>
+        <v>175900</v>
       </c>
       <c r="I54" s="3">
-        <v>168200</v>
+        <v>168700</v>
       </c>
       <c r="J54" s="3">
-        <v>164300</v>
+        <v>164700</v>
       </c>
       <c r="K54" s="3">
         <v>165400</v>
@@ -3145,25 +3145,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>29400</v>
+        <v>29500</v>
       </c>
       <c r="E57" s="3">
-        <v>29700</v>
+        <v>29800</v>
       </c>
       <c r="F57" s="3">
-        <v>35900</v>
+        <v>36000</v>
       </c>
       <c r="G57" s="3">
-        <v>32000</v>
+        <v>32100</v>
       </c>
       <c r="H57" s="3">
-        <v>36300</v>
+        <v>36400</v>
       </c>
       <c r="I57" s="3">
-        <v>30900</v>
+        <v>31000</v>
       </c>
       <c r="J57" s="3">
-        <v>32400</v>
+        <v>32500</v>
       </c>
       <c r="K57" s="3">
         <v>33300</v>
@@ -3201,25 +3201,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>34400</v>
+        <v>34500</v>
       </c>
       <c r="E58" s="3">
-        <v>44500</v>
+        <v>44600</v>
       </c>
       <c r="F58" s="3">
-        <v>45200</v>
+        <v>45400</v>
       </c>
       <c r="G58" s="3">
-        <v>43200</v>
+        <v>43300</v>
       </c>
       <c r="H58" s="3">
-        <v>39700</v>
+        <v>39800</v>
       </c>
       <c r="I58" s="3">
-        <v>34800</v>
+        <v>34900</v>
       </c>
       <c r="J58" s="3">
-        <v>28400</v>
+        <v>28500</v>
       </c>
       <c r="K58" s="3">
         <v>28200</v>
@@ -3263,16 +3263,16 @@
         <v>22700</v>
       </c>
       <c r="F59" s="3">
-        <v>21000</v>
+        <v>21100</v>
       </c>
       <c r="G59" s="3">
-        <v>18200</v>
+        <v>18300</v>
       </c>
       <c r="H59" s="3">
-        <v>18800</v>
+        <v>18900</v>
       </c>
       <c r="I59" s="3">
-        <v>12000</v>
+        <v>12100</v>
       </c>
       <c r="J59" s="3">
         <v>12200</v>
@@ -3313,25 +3313,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>82700</v>
+        <v>82900</v>
       </c>
       <c r="E60" s="3">
-        <v>96900</v>
+        <v>97200</v>
       </c>
       <c r="F60" s="3">
-        <v>102200</v>
+        <v>102500</v>
       </c>
       <c r="G60" s="3">
-        <v>93400</v>
+        <v>93700</v>
       </c>
       <c r="H60" s="3">
-        <v>94800</v>
+        <v>95100</v>
       </c>
       <c r="I60" s="3">
-        <v>77800</v>
+        <v>78000</v>
       </c>
       <c r="J60" s="3">
-        <v>73000</v>
+        <v>73200</v>
       </c>
       <c r="K60" s="3">
         <v>72400</v>
@@ -3384,7 +3384,7 @@
         <v>9400</v>
       </c>
       <c r="I61" s="3">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="J61" s="3">
         <v>11200</v>
@@ -3649,25 +3649,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>90400</v>
+        <v>90600</v>
       </c>
       <c r="E66" s="3">
-        <v>106300</v>
+        <v>106600</v>
       </c>
       <c r="F66" s="3">
-        <v>110600</v>
+        <v>110900</v>
       </c>
       <c r="G66" s="3">
-        <v>102600</v>
+        <v>102900</v>
       </c>
       <c r="H66" s="3">
-        <v>104900</v>
+        <v>105200</v>
       </c>
       <c r="I66" s="3">
-        <v>89400</v>
+        <v>89700</v>
       </c>
       <c r="J66" s="3">
-        <v>84800</v>
+        <v>85100</v>
       </c>
       <c r="K66" s="3">
         <v>83600</v>
@@ -3951,25 +3951,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>56300</v>
+        <v>56500</v>
       </c>
       <c r="E72" s="3">
-        <v>62800</v>
+        <v>63000</v>
       </c>
       <c r="F72" s="3">
-        <v>61300</v>
+        <v>61500</v>
       </c>
       <c r="G72" s="3">
-        <v>62900</v>
+        <v>63100</v>
       </c>
       <c r="H72" s="3">
-        <v>67000</v>
+        <v>67200</v>
       </c>
       <c r="I72" s="3">
-        <v>72800</v>
+        <v>73000</v>
       </c>
       <c r="J72" s="3">
-        <v>74000</v>
+        <v>74200</v>
       </c>
       <c r="K72" s="3">
         <v>76600</v>
@@ -4175,25 +4175,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>57500</v>
+        <v>57700</v>
       </c>
       <c r="E76" s="3">
-        <v>62500</v>
+        <v>62700</v>
       </c>
       <c r="F76" s="3">
-        <v>63100</v>
+        <v>63300</v>
       </c>
       <c r="G76" s="3">
-        <v>66500</v>
+        <v>66700</v>
       </c>
       <c r="H76" s="3">
-        <v>70500</v>
+        <v>70700</v>
       </c>
       <c r="I76" s="3">
-        <v>78800</v>
+        <v>79000</v>
       </c>
       <c r="J76" s="3">
-        <v>79400</v>
+        <v>79600</v>
       </c>
       <c r="K76" s="3">
         <v>81800</v>
@@ -4348,7 +4348,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6800</v>
+        <v>-6900</v>
       </c>
       <c r="E81" s="3">
         <v>1300</v>
@@ -4366,7 +4366,7 @@
         <v>100</v>
       </c>
       <c r="J81" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="K81" s="3">
         <v>200</v>
